--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -590,7 +590,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-immunization-vacine-codes</t>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-immunization-vaccine-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -875,7 +875,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-eimpf-medikationartanwendung.html</t>
+    <t>https://termgit.elga.gv.at/ValueSet/eimpf-medikationartanwendung</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1325,7 +1325,7 @@
     <t>The vaccine preventable disease the dose is being administered against.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/eimpf-impfrelevanteerkrankung</t>
+    <t>https://termgit.elga.gv.at/ValueSet/eimpf-immunizationtarget</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
@@ -1680,7 +1680,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.05859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="89.06640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>80</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>80</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
